--- a/questionnaire_templates/027_kitchen_style_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/027_kitchen_style_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1286,8 +1286,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'traditional'}</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Traditional'}</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rustic'}</t>
+          <t>rustic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rustic'}</t>
+          <t>Rustic</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'transitional'}</t>
+          <t>transitional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Transitional'}</t>
+          <t>Transitional</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'solid_surface'}</t>
+          <t>solid_surface</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Solid Surface'}</t>
+          <t>Solid Surface</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'laminate'}</t>
+          <t>laminate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Laminate'}</t>
+          <t>Laminate</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'engineered_stone'}</t>
+          <t>engineered_stone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Engineered Stone'}</t>
+          <t>Engineered Stone</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'granite'}</t>
+          <t>granite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Granite'}</t>
+          <t>Granite</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'increase_storage_space'}</t>
+          <t>increase_storage_space</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Increase Storage Space'}</t>
+          <t>Increase Storage Space</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'improve_aesthetics'}</t>
+          <t>improve_aesthetics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Improve Aesthetics'}</t>
+          <t>Improve Aesthetics</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'update_to_modernize'}</t>
+          <t>update_to_modernize</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Update to Modernize'}</t>
+          <t>Update to Modernize</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'led'}</t>
+          <t>led</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'LED'}</t>
+          <t>LED</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'recessed'}</t>
+          <t>recessed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Recessed'}</t>
+          <t>Recessed</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'under-cabinet'}</t>
+          <t>under-cabinet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Under-Cabinet'}</t>
+          <t>Under-Cabinet</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'pendant'}</t>
+          <t>pendant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Pendant'}</t>
+          <t>Pendant</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'full_kitchen'}</t>
+          <t>full_kitchen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Full Kitchen'}</t>
+          <t>Full Kitchen</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'partial_kitchen'}</t>
+          <t>partial_kitchen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Partial Kitchen'}</t>
+          <t>Partial Kitchen</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'u-shaped'}</t>
+          <t>u-shaped</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'U-Shaped'}</t>
+          <t>U-Shaped</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'l-shaped'}</t>
+          <t>l-shaped</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'L-Shaped'}</t>
+          <t>L-Shaped</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'linear'}</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Linear'}</t>
+          <t>Linear</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'galley'}</t>
+          <t>galley</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Galley'}</t>
+          <t>Galley</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'traditional'}</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Traditional'}</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'rustic'}</t>
+          <t>rustic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Rustic'}</t>
+          <t>Rustic</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'transitional'}</t>
+          <t>transitional</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Transitional'}</t>
+          <t>Transitional</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'stock'}</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Stock'}</t>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'semi-custom'}</t>
+          <t>semi-custom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Semi-Custom'}</t>
+          <t>Semi-Custom</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'built-in_appliances'}</t>
+          <t>built-in_appliances</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Built-in Appliances'}</t>
+          <t>Built-in Appliances</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'major_appliances'}</t>
+          <t>major_appliances</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Major Appliances'}</t>
+          <t>Major Appliances</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'minor_appliances'}</t>
+          <t>minor_appliances</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Minor Appliances'}</t>
+          <t>Minor Appliances</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'above_72_inches'}</t>
+          <t>above_72_inches</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Above 72 inches'}</t>
+          <t>Above 72 inches</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'48-72_inches'}</t>
+          <t>48-72_inches</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': '48-72 inches'}</t>
+          <t>48-72 inches</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'36-48_inches'}</t>
+          <t>36-48_inches</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': '36-48 inches'}</t>
+          <t>36-48 inches</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'below_36_inches'}</t>
+          <t>below_36_inches</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Below 36 inches'}</t>
+          <t>Below 36 inches</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'12-15_inches'}</t>
+          <t>12-15_inches</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': '12-15 inches'}</t>
+          <t>12-15 inches</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'18-21_inches'}</t>
+          <t>18-21_inches</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': '18-21 inches'}</t>
+          <t>18-21 inches</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'24-27_inches'}</t>
+          <t>24-27_inches</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': '24-27 inches'}</t>
+          <t>24-27 inches</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'30-33_inches'}</t>
+          <t>30-33_inches</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': '30-33 inches'}</t>
+          <t>30-33 inches</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'laminate'}</t>
+          <t>laminate</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Laminate'}</t>
+          <t>Laminate</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'solid_surface'}</t>
+          <t>solid_surface</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Solid Surface'}</t>
+          <t>Solid Surface</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'granite'}</t>
+          <t>granite</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Granite'}</t>
+          <t>Granite</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'marble'}</t>
+          <t>marble</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Marble'}</t>
+          <t>Marble</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'drop-in'}</t>
+          <t>drop-in</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Drop-in'}</t>
+          <t>Drop-in</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'under-mount'}</t>
+          <t>under-mount</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Under-Mount'}</t>
+          <t>Under-Mount</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'top-mount'}</t>
+          <t>top-mount</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Top-Mount'}</t>
+          <t>Top-Mount</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'single-handle'}</t>
+          <t>single-handle</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Single-Handle'}</t>
+          <t>Single-Handle</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'double-handle'}</t>
+          <t>double-handle</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Double-Handle'}</t>
+          <t>Double-Handle</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'wall-mount'}</t>
+          <t>wall-mount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Wall-Mount'}</t>
+          <t>Wall-Mount</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'wall-bridge'}</t>
+          <t>wall-bridge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Wall-Bridge'}</t>
+          <t>Wall-Bridge</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'stainless_steel'}</t>
+          <t>stainless_steel</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Stainless Steel'}</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'bronze'}</t>
+          <t>bronze</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Bronze'}</t>
+          <t>Bronze</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'brass'}</t>
+          <t>brass</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Brass'}</t>
+          <t>Brass</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'granite'}</t>
+          <t>granite</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Granite'}</t>
+          <t>Granite</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'marble'}</t>
+          <t>marble</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Marble'}</t>
+          <t>Marble</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'quartz'}</t>
+          <t>quartz</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Quartz'}</t>
+          <t>Quartz</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'hardwood'}</t>
+          <t>hardwood</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Hardwood'}</t>
+          <t>Hardwood</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'laminate'}</t>
+          <t>laminate</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Laminate'}</t>
+          <t>Laminate</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'ceramic'}</t>
+          <t>ceramic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Ceramic'}</t>
+          <t>Ceramic</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'vinyl'}</t>
+          <t>vinyl</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Vinyl'}</t>
+          <t>Vinyl</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'single-handle'}</t>
+          <t>single-handle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'Single-Handle'}</t>
+          <t>Single-Handle</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'single-handle_w/_touch_control'}</t>
+          <t>single-handle_w/_touch_control</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'Single-Handle w/ Touch Control'}</t>
+          <t>Single-Handle w/ Touch Control</t>
         </is>
       </c>
     </row>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'rectangle_w/_sink'}</t>
+          <t>rectangle_w/_sink</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Rectangle w/ Sink'}</t>
+          <t>Rectangle w/ Sink</t>
         </is>
       </c>
     </row>
@@ -2539,12 +2539,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'square_w/_sink'}</t>
+          <t>square_w/_sink</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Square w/ Sink'}</t>
+          <t>Square w/ Sink</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'round_w/_sink'}</t>
+          <t>round_w/_sink</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Round w/ Sink'}</t>
+          <t>Round w/ Sink</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'peninsula_w/_sink'}</t>
+          <t>peninsula_w/_sink</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'Peninsula w/ Sink'}</t>
+          <t>Peninsula w/ Sink</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'peninsula_w/_no_sink'}</t>
+          <t>peninsula_w/_no_sink</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 'Peninsula w/ No Sink'}</t>
+          <t>Peninsula w/ No Sink</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'tile'}</t>
+          <t>tile</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'Tile'}</t>
+          <t>Tile</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'painted'}</t>
+          <t>painted</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'Painted'}</t>
+          <t>Painted</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_'traditional'}</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 'Traditional'}</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_'rustic'}</t>
+          <t>rustic</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 'Rustic'}</t>
+          <t>Rustic</t>
         </is>
       </c>
     </row>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'transitional'}</t>
+          <t>transitional</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'Transitional'}</t>
+          <t>Transitional</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'label':_'hardwood'}</t>
+          <t>hardwood</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'label': 'Hardwood'}</t>
+          <t>Hardwood</t>
         </is>
       </c>
     </row>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'label':_'light_gray'}</t>
+          <t>light_gray</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'label': 'Light Gray'}</t>
+          <t>Light Gray</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'label':_'dark_gray'}</t>
+          <t>dark_gray</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'label': 'Dark Gray'}</t>
+          <t>Dark Gray</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'label':_'traditional'}</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'label': 'Traditional'}</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'label':_'rustic'}</t>
+          <t>rustic</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'label': 'Rustic'}</t>
+          <t>Rustic</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'label':_'transitional'}</t>
+          <t>transitional</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'label': 'Transitional'}</t>
+          <t>Transitional</t>
         </is>
       </c>
     </row>
